--- a/paper_replication_seed_results_enum.xlsx
+++ b/paper_replication_seed_results_enum.xlsx
@@ -515,7 +515,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="H2" t="n">
         <v>20</v>
@@ -551,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.147</v>
+        <v>0.146</v>
       </c>
       <c r="H3" t="n">
         <v>20</v>
@@ -587,7 +587,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.159</v>
+        <v>0.163</v>
       </c>
       <c r="H4" t="n">
         <v>20</v>
@@ -623,7 +623,7 @@
         <v>0.77</v>
       </c>
       <c r="G5" t="n">
-        <v>0.669</v>
+        <v>0.71</v>
       </c>
       <c r="H5" t="n">
         <v>35.9</v>
@@ -659,7 +659,7 @@
         <v>1.17</v>
       </c>
       <c r="G6" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="H6" t="n">
         <v>62.1</v>
@@ -695,7 +695,7 @@
         <v>1.37</v>
       </c>
       <c r="G7" t="n">
-        <v>3.072</v>
+        <v>3.412</v>
       </c>
       <c r="H7" t="n">
         <v>79.59999999999999</v>
@@ -731,7 +731,7 @@
         <v>2.69</v>
       </c>
       <c r="G8" t="n">
-        <v>3.86</v>
+        <v>4.241</v>
       </c>
       <c r="H8" t="n">
         <v>84.5</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1099157333374023</v>
+        <v>0.1041078567504883</v>
       </c>
       <c r="L2" t="n">
         <v>20</v>
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009996891021728516</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1069355010986328</v>
+        <v>0.102776050567627</v>
       </c>
       <c r="L3" t="n">
         <v>20</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1070847511291504</v>
+        <v>0.1036598682403564</v>
       </c>
       <c r="L4" t="n">
         <v>20</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.001000165939331055</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1031002998352051</v>
+        <v>0.1020801067352295</v>
       </c>
       <c r="L5" t="n">
         <v>20</v>
@@ -1057,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1041946411132812</v>
+        <v>0.1025724411010742</v>
       </c>
       <c r="L6" t="n">
         <v>20</v>
@@ -1102,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1043517589569092</v>
+        <v>0.1026003360748291</v>
       </c>
       <c r="L7" t="n">
         <v>20</v>
@@ -1147,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1083376407623291</v>
+        <v>0.1079211235046387</v>
       </c>
       <c r="L8" t="n">
         <v>20</v>
@@ -1192,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1105642318725586</v>
+        <v>0.10457444190979</v>
       </c>
       <c r="L9" t="n">
         <v>20</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1056315898895264</v>
+        <v>0.1060898303985596</v>
       </c>
       <c r="L10" t="n">
         <v>20</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1081423759460449</v>
+        <v>0.1050713062286377</v>
       </c>
       <c r="L11" t="n">
         <v>20</v>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.00107121467590332</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1726620197296143</v>
+        <v>0.140831470489502</v>
       </c>
       <c r="L12" t="n">
         <v>20</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1419351100921631</v>
+        <v>0.1444945335388184</v>
       </c>
       <c r="L13" t="n">
         <v>20</v>
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.0009939670562744141</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1477854251861572</v>
+        <v>0.1479566097259521</v>
       </c>
       <c r="L14" t="n">
         <v>20</v>
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.145866870880127</v>
+        <v>0.1446177959442139</v>
       </c>
       <c r="L15" t="n">
         <v>20</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00099945068359375</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1478486061096191</v>
+        <v>0.1484692096710205</v>
       </c>
       <c r="L16" t="n">
         <v>20</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1437294483184814</v>
+        <v>0.1450514793395996</v>
       </c>
       <c r="L17" t="n">
         <v>20</v>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001000165939331055</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1424727439880371</v>
+        <v>0.1419212818145752</v>
       </c>
       <c r="L18" t="n">
         <v>20</v>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1490428447723389</v>
+        <v>0.1662003993988037</v>
       </c>
       <c r="L19" t="n">
         <v>20</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1396822929382324</v>
+        <v>0.1391470432281494</v>
       </c>
       <c r="L20" t="n">
         <v>20</v>
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1416099071502686</v>
+        <v>0.1371073722839355</v>
       </c>
       <c r="L21" t="n">
         <v>20</v>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001015663146972656</v>
+        <v>0.001003503799438477</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1777,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1631147861480713</v>
+        <v>0.1601331233978271</v>
       </c>
       <c r="L22" t="n">
         <v>20</v>
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001503705978393555</v>
+        <v>0.001002073287963867</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1582093238830566</v>
+        <v>0.1606574058532715</v>
       </c>
       <c r="L23" t="n">
         <v>20</v>
@@ -1867,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1581275463104248</v>
+        <v>0.1551196575164795</v>
       </c>
       <c r="L24" t="n">
         <v>20</v>
@@ -1912,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1645267009735107</v>
+        <v>0.1643252372741699</v>
       </c>
       <c r="L25" t="n">
         <v>20</v>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.157564640045166</v>
+        <v>0.1596448421478271</v>
       </c>
       <c r="L26" t="n">
         <v>20</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.0005037784576416016</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.158843994140625</v>
+        <v>0.1573939323425293</v>
       </c>
       <c r="L27" t="n">
         <v>20</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1593117713928223</v>
+        <v>0.1636672019958496</v>
       </c>
       <c r="L28" t="n">
         <v>20</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.001002788543701172</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.157771110534668</v>
+        <v>0.1787970066070557</v>
       </c>
       <c r="L29" t="n">
         <v>20</v>
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1573164463043213</v>
+        <v>0.1639735698699951</v>
       </c>
       <c r="L30" t="n">
         <v>20</v>
@@ -2182,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1583075523376465</v>
+        <v>0.170236349105835</v>
       </c>
       <c r="L31" t="n">
         <v>20</v>
@@ -2227,7 +2227,7 @@
         <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5164880752563477</v>
+        <v>0.5295255184173584</v>
       </c>
       <c r="L32" t="n">
         <v>27</v>
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0009996891021728516</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>12</v>
@@ -2272,7 +2272,7 @@
         <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5289461612701416</v>
+        <v>0.5443475246429443</v>
       </c>
       <c r="L33" t="n">
         <v>28</v>
@@ -2317,7 +2317,7 @@
         <v>10</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7366793155670166</v>
+        <v>0.7828481197357178</v>
       </c>
       <c r="L34" t="n">
         <v>37</v>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.0009953975677490234</v>
       </c>
       <c r="H35" t="n">
         <v>11</v>
@@ -2362,7 +2362,7 @@
         <v>11</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5821394920349121</v>
+        <v>0.6327669620513916</v>
       </c>
       <c r="L35" t="n">
         <v>30</v>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.0009996891021728516</v>
       </c>
       <c r="H36" t="n">
         <v>12</v>
@@ -2407,7 +2407,7 @@
         <v>12</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6189417839050293</v>
+        <v>0.6175367832183838</v>
       </c>
       <c r="L36" t="n">
         <v>35</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0009996891021728516</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
         <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8249092102050781</v>
+        <v>0.7954230308532715</v>
       </c>
       <c r="L37" t="n">
         <v>41</v>
@@ -2497,7 +2497,7 @@
         <v>11</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6561174392700195</v>
+        <v>0.6622583866119385</v>
       </c>
       <c r="L38" t="n">
         <v>35</v>
@@ -2542,7 +2542,7 @@
         <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8380069732666016</v>
+        <v>0.9777629375457764</v>
       </c>
       <c r="L39" t="n">
         <v>47</v>
@@ -2587,7 +2587,7 @@
         <v>10</v>
       </c>
       <c r="K40" t="n">
-        <v>0.894193172454834</v>
+        <v>1.00020170211792</v>
       </c>
       <c r="L40" t="n">
         <v>51</v>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.001000404357910156</v>
       </c>
       <c r="H41" t="n">
         <v>11</v>
@@ -2632,7 +2632,7 @@
         <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>0.4956908226013184</v>
+        <v>0.5557498931884766</v>
       </c>
       <c r="L41" t="n">
         <v>28</v>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.001000165939331055</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>26</v>
@@ -2677,7 +2677,7 @@
         <v>26</v>
       </c>
       <c r="K42" t="n">
-        <v>1.374753475189209</v>
+        <v>1.485028266906738</v>
       </c>
       <c r="L42" t="n">
         <v>52</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0009996891021728516</v>
+        <v>0.0009987354278564453</v>
       </c>
       <c r="H43" t="n">
         <v>22</v>
@@ -2722,7 +2722,7 @@
         <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>1.789695262908936</v>
+        <v>2.076505899429321</v>
       </c>
       <c r="L43" t="n">
         <v>66</v>
@@ -2755,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.001007318496704102</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -2767,7 +2767,7 @@
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>1.419312477111816</v>
+        <v>1.560734272003174</v>
       </c>
       <c r="L44" t="n">
         <v>51</v>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.001001596450805664</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>22</v>
@@ -2812,7 +2812,7 @@
         <v>22</v>
       </c>
       <c r="K45" t="n">
-        <v>1.433482885360718</v>
+        <v>1.528716802597046</v>
       </c>
       <c r="L45" t="n">
         <v>51</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.0009984970092773438</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -2857,7 +2857,7 @@
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>1.796314239501953</v>
+        <v>1.935009717941284</v>
       </c>
       <c r="L46" t="n">
         <v>69</v>
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.001006126403808594</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -2902,7 +2902,7 @@
         <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>2.055451631546021</v>
+        <v>2.314157962799072</v>
       </c>
       <c r="L47" t="n">
         <v>82</v>
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0009996891021728516</v>
+        <v>0.001000404357910156</v>
       </c>
       <c r="H48" t="n">
         <v>25</v>
@@ -2947,7 +2947,7 @@
         <v>25</v>
       </c>
       <c r="K48" t="n">
-        <v>2.199272871017456</v>
+        <v>2.342173337936401</v>
       </c>
       <c r="L48" t="n">
         <v>80</v>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.00099945068359375</v>
+        <v>0.001000165939331055</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -2992,7 +2992,7 @@
         <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>1.627725124359131</v>
+        <v>1.830052852630615</v>
       </c>
       <c r="L49" t="n">
         <v>59</v>
@@ -3037,7 +3037,7 @@
         <v>23</v>
       </c>
       <c r="K50" t="n">
-        <v>1.828150033950806</v>
+        <v>2.076738595962524</v>
       </c>
       <c r="L50" t="n">
         <v>65</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.00099945068359375</v>
+        <v>0.0009944438934326172</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -3082,7 +3082,7 @@
         <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>1.277950525283813</v>
+        <v>1.348145484924316</v>
       </c>
       <c r="L51" t="n">
         <v>46</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.001015424728393555</v>
+        <v>0.001009702682495117</v>
       </c>
       <c r="H52" t="n">
         <v>39</v>
@@ -3127,7 +3127,7 @@
         <v>39</v>
       </c>
       <c r="K52" t="n">
-        <v>2.571268320083618</v>
+        <v>2.712070465087891</v>
       </c>
       <c r="L52" t="n">
         <v>63</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.0009999275207519531</v>
       </c>
       <c r="H53" t="n">
         <v>39</v>
@@ -3172,7 +3172,7 @@
         <v>39</v>
       </c>
       <c r="K53" t="n">
-        <v>2.436725378036499</v>
+        <v>2.700953722000122</v>
       </c>
       <c r="L53" t="n">
         <v>60</v>
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.001000404357910156</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>36</v>
@@ -3217,7 +3217,7 @@
         <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>4.11334753036499</v>
+        <v>4.400927543640137</v>
       </c>
       <c r="L54" t="n">
         <v>107</v>
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0009865760803222656</v>
+        <v>0.00100398063659668</v>
       </c>
       <c r="H55" t="n">
         <v>41</v>
@@ -3262,7 +3262,7 @@
         <v>41</v>
       </c>
       <c r="K55" t="n">
-        <v>3.554033041000366</v>
+        <v>3.744375944137573</v>
       </c>
       <c r="L55" t="n">
         <v>93</v>
@@ -3295,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.001511812210083008</v>
+        <v>0.0009844303131103516</v>
       </c>
       <c r="H56" t="n">
         <v>39</v>
@@ -3307,7 +3307,7 @@
         <v>39</v>
       </c>
       <c r="K56" t="n">
-        <v>2.967473268508911</v>
+        <v>3.276848554611206</v>
       </c>
       <c r="L56" t="n">
         <v>75</v>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.001016139984130859</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>39</v>
@@ -3352,7 +3352,7 @@
         <v>39</v>
       </c>
       <c r="K57" t="n">
-        <v>3.949277400970459</v>
+        <v>4.318600177764893</v>
       </c>
       <c r="L57" t="n">
         <v>105</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0009992122650146484</v>
+        <v>0.0009980201721191406</v>
       </c>
       <c r="H58" t="n">
         <v>40</v>
@@ -3397,7 +3397,7 @@
         <v>40</v>
       </c>
       <c r="K58" t="n">
-        <v>2.653370380401611</v>
+        <v>2.852726936340332</v>
       </c>
       <c r="L58" t="n">
         <v>64</v>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0009937286376953125</v>
+        <v>0.00101470947265625</v>
       </c>
       <c r="H59" t="n">
         <v>41</v>
@@ -3442,7 +3442,7 @@
         <v>41</v>
       </c>
       <c r="K59" t="n">
-        <v>2.890284061431885</v>
+        <v>3.41883659362793</v>
       </c>
       <c r="L59" t="n">
         <v>80</v>
@@ -3475,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0009975433349609375</v>
+        <v>0.0009992122650146484</v>
       </c>
       <c r="H60" t="n">
         <v>38</v>
@@ -3487,7 +3487,7 @@
         <v>38</v>
       </c>
       <c r="K60" t="n">
-        <v>3.07451868057251</v>
+        <v>3.897647619247437</v>
       </c>
       <c r="L60" t="n">
         <v>80</v>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.001513957977294922</v>
+        <v>0.001000165939331055</v>
       </c>
       <c r="H61" t="n">
         <v>39</v>
@@ -3532,7 +3532,7 @@
         <v>39</v>
       </c>
       <c r="K61" t="n">
-        <v>2.510638952255249</v>
+        <v>2.797741651535034</v>
       </c>
       <c r="L61" t="n">
         <v>69</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.001012086868286133</v>
+        <v>0.001007080078125</v>
       </c>
       <c r="H62" t="n">
         <v>52</v>
@@ -3577,7 +3577,7 @@
         <v>52</v>
       </c>
       <c r="K62" t="n">
-        <v>2.521245956420898</v>
+        <v>2.799473524093628</v>
       </c>
       <c r="L62" t="n">
         <v>53</v>
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.0009996891021728516</v>
       </c>
       <c r="H63" t="n">
         <v>46</v>
@@ -3622,7 +3622,7 @@
         <v>46</v>
       </c>
       <c r="K63" t="n">
-        <v>4.947266340255737</v>
+        <v>5.561593770980835</v>
       </c>
       <c r="L63" t="n">
         <v>113</v>
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0009999275207519531</v>
+        <v>0.0009996891021728516</v>
       </c>
       <c r="H64" t="n">
         <v>46</v>
@@ -3667,7 +3667,7 @@
         <v>46</v>
       </c>
       <c r="K64" t="n">
-        <v>3.57687520980835</v>
+        <v>3.889286041259766</v>
       </c>
       <c r="L64" t="n">
         <v>77</v>
@@ -3700,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>0.0009875297546386719</v>
       </c>
       <c r="H65" t="n">
         <v>46</v>
@@ -3712,7 +3712,7 @@
         <v>46</v>
       </c>
       <c r="K65" t="n">
-        <v>3.600994348526001</v>
+        <v>4.298353672027588</v>
       </c>
       <c r="L65" t="n">
         <v>81</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0009925365447998047</v>
+        <v>0.00100398063659668</v>
       </c>
       <c r="H66" t="n">
         <v>51</v>
@@ -3757,7 +3757,7 @@
         <v>51</v>
       </c>
       <c r="K66" t="n">
-        <v>2.496912240982056</v>
+        <v>2.656984806060791</v>
       </c>
       <c r="L66" t="n">
         <v>53</v>
@@ -3790,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.001000165939331055</v>
+        <v>0.001006841659545898</v>
       </c>
       <c r="H67" t="n">
         <v>46</v>
@@ -3802,7 +3802,7 @@
         <v>46</v>
       </c>
       <c r="K67" t="n">
-        <v>5.245676517486572</v>
+        <v>5.5807204246521</v>
       </c>
       <c r="L67" t="n">
         <v>117</v>
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.001000404357910156</v>
+        <v>0.001009941101074219</v>
       </c>
       <c r="H68" t="n">
         <v>45</v>
@@ -3847,7 +3847,7 @@
         <v>45</v>
       </c>
       <c r="K68" t="n">
-        <v>6.485848665237427</v>
+        <v>7.119297027587891</v>
       </c>
       <c r="L68" t="n">
         <v>146</v>
@@ -3880,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.001510381698608398</v>
+        <v>0.0009999275207519531</v>
       </c>
       <c r="H69" t="n">
         <v>52</v>
@@ -3892,7 +3892,7 @@
         <v>52</v>
       </c>
       <c r="K69" t="n">
-        <v>2.962764024734497</v>
+        <v>3.281545400619507</v>
       </c>
       <c r="L69" t="n">
         <v>66</v>
@@ -3925,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.001513004302978516</v>
+        <v>0.001007318496704102</v>
       </c>
       <c r="H70" t="n">
         <v>50</v>
@@ -3937,7 +3937,7 @@
         <v>50</v>
       </c>
       <c r="K70" t="n">
-        <v>3.535699844360352</v>
+        <v>3.714770317077637</v>
       </c>
       <c r="L70" t="n">
         <v>73</v>
@@ -3970,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.001013755798339844</v>
+        <v>0.0009999275207519531</v>
       </c>
       <c r="H71" t="n">
         <v>50</v>
@@ -3982,7 +3982,7 @@
         <v>50</v>
       </c>
       <c r="K71" t="n">
-        <v>3.223203420639038</v>
+        <v>3.50946307182312</v>
       </c>
       <c r="L71" t="n">
         <v>66</v>
@@ -4084,7 +4084,7 @@
         <v>1.14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>10.6</v>
@@ -4093,7 +4093,7 @@
         <v>0.49</v>
       </c>
       <c r="G2" t="n">
-        <v>0.555</v>
+        <v>0.585</v>
       </c>
       <c r="H2" t="n">
         <v>31.6</v>
@@ -4122,7 +4122,7 @@
         <v>1.28</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E3" t="n">
         <v>18.6</v>
@@ -4131,7 +4131,7 @@
         <v>1.28</v>
       </c>
       <c r="G3" t="n">
-        <v>1.214</v>
+        <v>1.299</v>
       </c>
       <c r="H3" t="n">
         <v>51.6</v>
@@ -4169,7 +4169,7 @@
         <v>2.69</v>
       </c>
       <c r="G4" t="n">
-        <v>3.799</v>
+        <v>4.142</v>
       </c>
       <c r="H4" t="n">
         <v>84.5</v>
@@ -4207,7 +4207,7 @@
         <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>5.267</v>
+        <v>5.603</v>
       </c>
       <c r="H5" t="n">
         <v>96.8</v>
@@ -4343,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00151515007019043</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>11</v>
@@ -4355,7 +4355,7 @@
         <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6820969581604004</v>
+        <v>0.7147905826568604</v>
       </c>
       <c r="L2" t="n">
         <v>42</v>
@@ -4390,7 +4390,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.001001119613647461</v>
       </c>
       <c r="H3" t="n">
         <v>11</v>
@@ -4402,7 +4402,7 @@
         <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5280885696411133</v>
+        <v>0.5705811977386475</v>
       </c>
       <c r="L3" t="n">
         <v>31</v>
@@ -4437,7 +4437,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001019954681396484</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>11</v>
@@ -4449,7 +4449,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>0.472928524017334</v>
+        <v>0.4815354347229004</v>
       </c>
       <c r="L4" t="n">
         <v>27</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6198849678039551</v>
+        <v>0.6326839923858643</v>
       </c>
       <c r="L5" t="n">
         <v>34</v>
@@ -4543,7 +4543,7 @@
         <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4258797168731689</v>
+        <v>0.4294188022613525</v>
       </c>
       <c r="L6" t="n">
         <v>25</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001025199890136719</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -4590,7 +4590,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>0.753504753112793</v>
+        <v>0.7887270450592041</v>
       </c>
       <c r="L7" t="n">
         <v>39</v>
@@ -4625,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001509904861450195</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>10</v>
@@ -4637,7 +4637,7 @@
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4819550514221191</v>
+        <v>0.5555391311645508</v>
       </c>
       <c r="L8" t="n">
         <v>28</v>
@@ -4684,7 +4684,7 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>0.632361888885498</v>
+        <v>0.6607692241668701</v>
       </c>
       <c r="L9" t="n">
         <v>34</v>
@@ -4731,7 +4731,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>0.454190731048584</v>
+        <v>0.4860875606536865</v>
       </c>
       <c r="L10" t="n">
         <v>27</v>
@@ -4766,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.001001834869384766</v>
       </c>
       <c r="H11" t="n">
         <v>11</v>
@@ -4778,7 +4778,7 @@
         <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4980247020721436</v>
+        <v>0.5316786766052246</v>
       </c>
       <c r="L11" t="n">
         <v>29</v>
@@ -4813,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.00099945068359375</v>
       </c>
       <c r="H12" t="n">
         <v>20</v>
@@ -4825,7 +4825,7 @@
         <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9665241241455078</v>
+        <v>1.030442714691162</v>
       </c>
       <c r="L12" t="n">
         <v>45</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.001009225845336914</v>
       </c>
       <c r="H13" t="n">
         <v>19</v>
@@ -4872,7 +4872,7 @@
         <v>19</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8879001140594482</v>
+        <v>0.9615201950073242</v>
       </c>
       <c r="L13" t="n">
         <v>37</v>
@@ -4919,7 +4919,7 @@
         <v>19</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9916031360626221</v>
+        <v>1.074236154556274</v>
       </c>
       <c r="L14" t="n">
         <v>43</v>
@@ -4966,7 +4966,7 @@
         <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>1.663905382156372</v>
+        <v>1.906389474868774</v>
       </c>
       <c r="L15" t="n">
         <v>77</v>
@@ -5001,7 +5001,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.001003265380859375</v>
       </c>
       <c r="H16" t="n">
         <v>18</v>
@@ -5013,7 +5013,7 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>1.140039920806885</v>
+        <v>1.228690624237061</v>
       </c>
       <c r="L16" t="n">
         <v>49</v>
@@ -5060,7 +5060,7 @@
         <v>18</v>
       </c>
       <c r="K17" t="n">
-        <v>1.129982948303223</v>
+        <v>1.226999998092651</v>
       </c>
       <c r="L17" t="n">
         <v>42</v>
@@ -5107,7 +5107,7 @@
         <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>1.763672828674316</v>
+        <v>1.857674598693848</v>
       </c>
       <c r="L18" t="n">
         <v>67</v>
@@ -5154,7 +5154,7 @@
         <v>19</v>
       </c>
       <c r="K19" t="n">
-        <v>1.701613664627075</v>
+        <v>1.746253490447998</v>
       </c>
       <c r="L19" t="n">
         <v>70</v>
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.001000642776489258</v>
       </c>
       <c r="H20" t="n">
         <v>21</v>
@@ -5201,7 +5201,7 @@
         <v>21</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5352587699890137</v>
+        <v>0.5571236610412598</v>
       </c>
       <c r="L20" t="n">
         <v>24</v>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.001001596450805664</v>
       </c>
       <c r="H21" t="n">
         <v>18</v>
@@ -5248,7 +5248,7 @@
         <v>18</v>
       </c>
       <c r="K21" t="n">
-        <v>1.360163450241089</v>
+        <v>1.405331134796143</v>
       </c>
       <c r="L21" t="n">
         <v>62</v>
@@ -5283,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001001596450805664</v>
+        <v>0.0009989738464355469</v>
       </c>
       <c r="H22" t="n">
         <v>52</v>
@@ -5295,7 +5295,7 @@
         <v>52</v>
       </c>
       <c r="K22" t="n">
-        <v>2.537942886352539</v>
+        <v>2.843669414520264</v>
       </c>
       <c r="L22" t="n">
         <v>53</v>
@@ -5330,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001000165939331055</v>
+        <v>0.002509593963623047</v>
       </c>
       <c r="H23" t="n">
         <v>46</v>
@@ -5342,7 +5342,7 @@
         <v>46</v>
       </c>
       <c r="K23" t="n">
-        <v>4.923689365386963</v>
+        <v>5.352534055709839</v>
       </c>
       <c r="L23" t="n">
         <v>113</v>
@@ -5377,7 +5377,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001510858535766602</v>
+        <v>0.001000642776489258</v>
       </c>
       <c r="H24" t="n">
         <v>46</v>
@@ -5389,7 +5389,7 @@
         <v>46</v>
       </c>
       <c r="K24" t="n">
-        <v>3.59180474281311</v>
+        <v>3.788744449615479</v>
       </c>
       <c r="L24" t="n">
         <v>77</v>
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0009944438934326172</v>
+        <v>0.001001596450805664</v>
       </c>
       <c r="H25" t="n">
         <v>46</v>
@@ -5436,7 +5436,7 @@
         <v>46</v>
       </c>
       <c r="K25" t="n">
-        <v>3.835437297821045</v>
+        <v>3.928039073944092</v>
       </c>
       <c r="L25" t="n">
         <v>81</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00151371955871582</v>
+        <v>0.001001119613647461</v>
       </c>
       <c r="H26" t="n">
         <v>51</v>
@@ -5483,7 +5483,7 @@
         <v>51</v>
       </c>
       <c r="K26" t="n">
-        <v>2.477487087249756</v>
+        <v>2.597357511520386</v>
       </c>
       <c r="L26" t="n">
         <v>53</v>
@@ -5518,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0009868144989013672</v>
+        <v>0.001003742218017578</v>
       </c>
       <c r="H27" t="n">
         <v>46</v>
@@ -5530,7 +5530,7 @@
         <v>46</v>
       </c>
       <c r="K27" t="n">
-        <v>4.922820568084717</v>
+        <v>5.73363184928894</v>
       </c>
       <c r="L27" t="n">
         <v>117</v>
@@ -5565,7 +5565,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0009996891021728516</v>
+        <v>0.001001119613647461</v>
       </c>
       <c r="H28" t="n">
         <v>45</v>
@@ -5577,7 +5577,7 @@
         <v>45</v>
       </c>
       <c r="K28" t="n">
-        <v>6.35619044303894</v>
+        <v>6.844882726669312</v>
       </c>
       <c r="L28" t="n">
         <v>146</v>
@@ -5612,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.001004219055175781</v>
       </c>
       <c r="H29" t="n">
         <v>52</v>
@@ -5624,7 +5624,7 @@
         <v>52</v>
       </c>
       <c r="K29" t="n">
-        <v>2.967516660690308</v>
+        <v>3.170607328414917</v>
       </c>
       <c r="L29" t="n">
         <v>66</v>
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0005178451538085938</v>
+        <v>0.001017332077026367</v>
       </c>
       <c r="H30" t="n">
         <v>50</v>
@@ -5671,7 +5671,7 @@
         <v>50</v>
       </c>
       <c r="K30" t="n">
-        <v>3.31460165977478</v>
+        <v>3.642305135726929</v>
       </c>
       <c r="L30" t="n">
         <v>73</v>
@@ -5706,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0009953975677490234</v>
+        <v>0.0009989738464355469</v>
       </c>
       <c r="H31" t="n">
         <v>50</v>
@@ -5718,7 +5718,7 @@
         <v>50</v>
       </c>
       <c r="K31" t="n">
-        <v>3.058217287063599</v>
+        <v>3.513281583786011</v>
       </c>
       <c r="L31" t="n">
         <v>66</v>
@@ -5753,7 +5753,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.001580715179443359</v>
       </c>
       <c r="H32" t="n">
         <v>62</v>
@@ -5765,7 +5765,7 @@
         <v>62</v>
       </c>
       <c r="K32" t="n">
-        <v>7.011955738067627</v>
+        <v>7.526842355728149</v>
       </c>
       <c r="L32" t="n">
         <v>129</v>
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0005090236663818359</v>
+        <v>0.0009992122650146484</v>
       </c>
       <c r="H33" t="n">
         <v>63</v>
@@ -5812,7 +5812,7 @@
         <v>63</v>
       </c>
       <c r="K33" t="n">
-        <v>5.164093971252441</v>
+        <v>5.33542537689209</v>
       </c>
       <c r="L33" t="n">
         <v>96</v>
@@ -5847,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.002007246017456055</v>
+        <v>0.001000165939331055</v>
       </c>
       <c r="H34" t="n">
         <v>65</v>
@@ -5859,7 +5859,7 @@
         <v>65</v>
       </c>
       <c r="K34" t="n">
-        <v>5.163767576217651</v>
+        <v>5.335745573043823</v>
       </c>
       <c r="L34" t="n">
         <v>90</v>
@@ -5894,7 +5894,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.001002073287963867</v>
+        <v>0.0005185604095458984</v>
       </c>
       <c r="H35" t="n">
         <v>59</v>
@@ -5906,7 +5906,7 @@
         <v>59</v>
       </c>
       <c r="K35" t="n">
-        <v>6.299755573272705</v>
+        <v>6.84074330329895</v>
       </c>
       <c r="L35" t="n">
         <v>117</v>
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00099945068359375</v>
+        <v>0.002006769180297852</v>
       </c>
       <c r="H36" t="n">
         <v>64</v>
@@ -5953,7 +5953,7 @@
         <v>64</v>
       </c>
       <c r="K36" t="n">
-        <v>6.117688417434692</v>
+        <v>6.453686475753784</v>
       </c>
       <c r="L36" t="n">
         <v>116</v>
@@ -5988,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0005075931549072266</v>
+        <v>0.0009992122650146484</v>
       </c>
       <c r="H37" t="n">
         <v>70</v>
@@ -6000,7 +6000,7 @@
         <v>70</v>
       </c>
       <c r="K37" t="n">
-        <v>2.630045890808105</v>
+        <v>2.838277101516724</v>
       </c>
       <c r="L37" t="n">
         <v>47</v>
@@ -6035,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.00100398063659668</v>
+        <v>0.0005207061767578125</v>
       </c>
       <c r="H38" t="n">
         <v>66</v>
@@ -6047,7 +6047,7 @@
         <v>66</v>
       </c>
       <c r="K38" t="n">
-        <v>4.289806604385376</v>
+        <v>5.100301504135132</v>
       </c>
       <c r="L38" t="n">
         <v>80</v>
@@ -6082,7 +6082,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0019989013671875</v>
+        <v>0.0019378662109375</v>
       </c>
       <c r="H39" t="n">
         <v>64</v>
@@ -6094,7 +6094,7 @@
         <v>64</v>
       </c>
       <c r="K39" t="n">
-        <v>6.698392868041992</v>
+        <v>7.21213960647583</v>
       </c>
       <c r="L39" t="n">
         <v>122</v>
@@ -6129,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0009999275207519531</v>
+        <v>0.00200653076171875</v>
       </c>
       <c r="H40" t="n">
         <v>63</v>
@@ -6141,7 +6141,7 @@
         <v>63</v>
       </c>
       <c r="K40" t="n">
-        <v>6.141268491744995</v>
+        <v>6.152579307556152</v>
       </c>
       <c r="L40" t="n">
         <v>116</v>
@@ -6176,7 +6176,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.001007080078125</v>
+        <v>0.001000165939331055</v>
       </c>
       <c r="H41" t="n">
         <v>65</v>
@@ -6188,7 +6188,7 @@
         <v>65</v>
       </c>
       <c r="K41" t="n">
-        <v>3.153415679931641</v>
+        <v>3.231939792633057</v>
       </c>
       <c r="L41" t="n">
         <v>55</v>
